--- a/tests/samples/school_roster.xlsx
+++ b/tests/samples/school_roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Projects\contacts manager\tests\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F55EE871-EA08-49E5-BB4C-A17F67870AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC3B82B5-2721-406A-866C-17094DE917C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="14400" windowHeight="7360" xr2:uid="{58259EF6-1EBC-42B3-969B-DB4DC1C25E48}"/>
+    <workbookView xWindow="1480" yWindow="1480" windowWidth="14400" windowHeight="7360" xr2:uid="{D04130F1-F763-426C-A96D-06B55F711F33}"/>
   </bookViews>
   <sheets>
     <sheet name="الكشف" sheetId="1" r:id="rId1"/>
@@ -478,7 +478,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C24383-5CB4-4EE0-843E-8A3A9ACEB363}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBDACA4-8924-4B6C-917E-7D5A144CE737}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
